--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas-web\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="telefonos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Nombre</t>
   </si>
@@ -47,56 +47,41 @@
     <t>Vida</t>
   </si>
   <si>
+    <t>2 años</t>
+  </si>
+  <si>
+    <t>Macho</t>
+  </si>
+  <si>
+    <t>mestizo</t>
+  </si>
+  <si>
+    <t>Joan</t>
+  </si>
+  <si>
+    <t>Cuando Vida era cachorro, no podía mover las patas traseras y se arrastraba. Había recibido un disparo de balín en la espalda. La rescatamos y la llevamos urgentemente al veterinario para valorar la lesión._x000d_
+_x000d_
+Gracias a los donativos de muchas personas, Vida pudo ser operado. No tenía una lesión medular, pero las secuelas del hematoma que se produjo tras el impacto hicieron necesaria una rehabilitación especializada para ayudarle a recuperar movilidad y avanzar hacia una vida plena._x000d_
+_x000d__x000d_
+Una vez Vida se haya recuperado esperamos encontrar una familia que pueda ofrecerle todo el cariño que se merece. Por el momento puedes apadrinarla o participar en nuestra rifa solidaria para financiar su tratamiento médico</t>
+  </si>
+  <si>
+    <t>Negra</t>
+  </si>
+  <si>
+    <t>20 meses</t>
+  </si>
+  <si>
     <t>Hembra</t>
   </si>
   <si>
-    <t>mestizo</t>
-  </si>
-  <si>
-    <t>Judith</t>
-  </si>
-  <si>
-    <t>Cuando Vida era cachorro, no podía mover las patas traseras y se arrastraba. Había recibido un disparo de balín en la espalda. La rescatamos y la llevamos urgentemente al veterinario para valorar la lesión._x000D_
-_x000D_
-Gracias a los donativos de muchas personas, Vida pudo ser operado. No tenía una lesión medular, pero las secuelas del hematoma que se produjo tras el impacto hicieron necesaria una rehabilitación especializada para ayudarle a recuperar movilidad y avanzar hacia una vida plena._x000D_
-_x000D__x000D_
-Una vez Vida se haya recuperado esperamos encontrar una familia que pueda ofrecerle todo el cariño que se merece. Por el momento puedes apadrinarla o participar en nuestra rifa solidaria para financiar su tratamiento médico</t>
-  </si>
-  <si>
-    <t>hembra mix yorki</t>
-  </si>
-  <si>
-    <t>Sira</t>
-  </si>
-  <si>
-    <t>Zule</t>
-  </si>
-  <si>
-    <t>zule</t>
-  </si>
-  <si>
-    <t>Joan</t>
-  </si>
-  <si>
-    <t>Hera</t>
-  </si>
-  <si>
-    <t>hera</t>
-  </si>
-  <si>
-    <t>Negra</t>
-  </si>
-  <si>
-    <t>20 meses</t>
-  </si>
-  <si>
     <t>mix mastín</t>
   </si>
   <si>
     <t>negra</t>
   </si>
   <si>
-    <t>Se lleva bien con perros y personas_x000D_
+    <t>Se lleva bien con perros y personas_x000d_
 Muy buena y obediente</t>
   </si>
   <si>
@@ -106,122 +91,155 @@
     <t>4 años</t>
   </si>
   <si>
-    <t>Macho</t>
-  </si>
-  <si>
     <t>mix Border collie</t>
   </si>
   <si>
     <t>tayson</t>
   </si>
   <si>
-    <t>Ha subido conviviendo con gatos , perros y niños._x000D_
-Pesar alrededor de 14 kg y no hay masa de cresa_x000D_
+    <t>Ha subido conviviendo con gatos , perros y niños._x000d_
+Pesar alrededor de 14 kg y no hay masa de cresa_x000d_
 Está en Cádiz pero puede viajar a casi toda España con nuestros transportistas de animales</t>
   </si>
   <si>
-    <t>Camada</t>
-  </si>
-  <si>
-    <t>camada amerian standfor pitbull</t>
-  </si>
-  <si>
-    <t>Carpeta</t>
-  </si>
-  <si>
-    <t>camada bodeguero breton</t>
-  </si>
-  <si>
-    <t>Blondy</t>
-  </si>
-  <si>
-    <t>blondy</t>
-  </si>
-  <si>
-    <t>Lesa</t>
-  </si>
-  <si>
-    <t>lesa</t>
-  </si>
-  <si>
-    <t>Azul y Verde</t>
-  </si>
-  <si>
-    <t>azul y verde</t>
-  </si>
-  <si>
-    <t>Dina</t>
-  </si>
-  <si>
-    <t>dina</t>
-  </si>
-  <si>
-    <t>Alba</t>
-  </si>
-  <si>
-    <t>alba</t>
-  </si>
-  <si>
-    <t>Duende</t>
-  </si>
-  <si>
-    <t>duende</t>
-  </si>
-  <si>
-    <t>Balú</t>
-  </si>
-  <si>
-    <t>balu</t>
-  </si>
-  <si>
-    <t>Camada podenco pastor aleman</t>
-  </si>
-  <si>
-    <t>camada podenco pastor aleman</t>
-  </si>
-  <si>
-    <t>Toby</t>
-  </si>
-  <si>
-    <t>toby</t>
-  </si>
-  <si>
-    <t>Nico</t>
-  </si>
-  <si>
-    <t>nico</t>
-  </si>
-  <si>
-    <t>Loli</t>
-  </si>
-  <si>
-    <t>2 años</t>
-  </si>
-  <si>
     <t>Merlo</t>
   </si>
   <si>
+    <t>2 semanas</t>
+  </si>
+  <si>
+    <t>mix Podenco</t>
+  </si>
+  <si>
     <t>merlo</t>
-  </si>
-  <si>
-    <t>mix Podenco</t>
-  </si>
-  <si>
-    <t>2 semanas</t>
   </si>
   <si>
     <t>La madre es un podenco maneto y se desconoce al padre.
 Se entrega con protocolo veterinario completo y puede viajar a casi toda España</t>
   </si>
   <si>
+    <t>Carpeta</t>
+  </si>
+  <si>
+    <t>Camada</t>
+  </si>
+  <si>
+    <t>camada bodeguero breton</t>
+  </si>
+  <si>
+    <t>Blondy</t>
+  </si>
+  <si>
+    <t>blondy</t>
+  </si>
+  <si>
+    <t>Lesa</t>
+  </si>
+  <si>
+    <t>lesa</t>
+  </si>
+  <si>
+    <t>Azul y Verde</t>
+  </si>
+  <si>
+    <t>azul y verde</t>
+  </si>
+  <si>
+    <t>Dina</t>
+  </si>
+  <si>
+    <t>dina</t>
+  </si>
+  <si>
+    <t>Alba</t>
+  </si>
+  <si>
+    <t>alba</t>
+  </si>
+  <si>
+    <t>Duende</t>
+  </si>
+  <si>
+    <t>duende</t>
+  </si>
+  <si>
+    <t>Balú</t>
+  </si>
+  <si>
+    <t>balu</t>
+  </si>
+  <si>
+    <t>Camada podenco pastor aleman</t>
+  </si>
+  <si>
+    <t>camada podenco pastor aleman</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>toby</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>nico</t>
+  </si>
+  <si>
+    <t>Zule</t>
+  </si>
+  <si>
+    <t>zule</t>
+  </si>
+  <si>
+    <t>Loli</t>
+  </si>
+  <si>
+    <t>hembra mix yorki</t>
+  </si>
+  <si>
+    <t>Hera</t>
+  </si>
+  <si>
+    <t>hera</t>
+  </si>
+  <si>
     <t>Camada amerian standfor y pitbull</t>
+  </si>
+  <si>
+    <t>camada amerian standfor pitbull</t>
+  </si>
+  <si>
+    <t>Mika</t>
+  </si>
+  <si>
+    <t>mika</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>dante</t>
+  </si>
+  <si>
+    <t>Bambi</t>
+  </si>
+  <si>
+    <t>bambi</t>
+  </si>
+  <si>
+    <t>Sira</t>
+  </si>
+  <si>
+    <t>Judith</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -233,21 +251,13 @@
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -263,60 +273,43 @@
     </fill>
   </fills>
   <borders count="2">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
     <cellStyle name="HeaderStyle" xfId="2"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -325,10 +318,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -604,22 +597,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
-    <col min="5" max="6" width="13.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="177" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.85547" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.85547" style="1" customWidth="1"/>
+    <col min="7" max="7" width="177" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -638,100 +628,100 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="114" customHeight="1">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" ht="30">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -740,143 +730,166 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="66" style="3" customWidth="1"/>
+    <col min="1" max="1" width="27.42578" customWidth="1"/>
+    <col min="2" max="2" width="36.57031" customWidth="1"/>
+    <col min="3" max="3" width="17.85547" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.57031" style="1" customWidth="1"/>
+    <col min="5" max="5" width="66" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6">
+      <c r="A6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9">
+      <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10">
+      <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11">
+      <c r="A11" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12">
+      <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13">
+      <c r="A13" t="s">
         <v>52</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -885,32 +898,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B1">
         <v>649776448</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>692160589</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>608678808</v>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas.github.io\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="telefonos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
   <si>
     <t>Nombre</t>
   </si>
@@ -59,10 +59,10 @@
     <t>Joan</t>
   </si>
   <si>
-    <t>Cuando Vida era cachorro, no podía mover las patas traseras y se arrastraba. Había recibido un disparo de balín en la espalda. La rescatamos y la llevamos urgentemente al veterinario para valorar la lesión._x000d_
-_x000d_
-Gracias a los donativos de muchas personas, Vida pudo ser operado. No tenía una lesión medular, pero las secuelas del hematoma que se produjo tras el impacto hicieron necesaria una rehabilitación especializada para ayudarle a recuperar movilidad y avanzar hacia una vida plena._x000d_
-_x000d__x000d_
+    <t>Cuando Vida era cachorro, no podía mover las patas traseras y se arrastraba. Había recibido un disparo de balín en la espalda. La rescatamos y la llevamos urgentemente al veterinario para valorar la lesión._x000D_
+_x000D_
+Gracias a los donativos de muchas personas, Vida pudo ser operado. No tenía una lesión medular, pero las secuelas del hematoma que se produjo tras el impacto hicieron necesaria una rehabilitación especializada para ayudarle a recuperar movilidad y avanzar hacia una vida plena._x000D_
+_x000D__x000D_
 Una vez Vida se haya recuperado esperamos encontrar una familia que pueda ofrecerle todo el cariño que se merece. Por el momento puedes apadrinarla o participar en nuestra rifa solidaria para financiar su tratamiento médico</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t>negra</t>
   </si>
   <si>
-    <t>Se lleva bien con perros y personas_x000d_
+    <t>Se lleva bien con perros y personas_x000D_
 Muy buena y obediente</t>
   </si>
   <si>
@@ -97,27 +97,17 @@
     <t>tayson</t>
   </si>
   <si>
-    <t>Ha subido conviviendo con gatos , perros y niños._x000d_
-Pesar alrededor de 14 kg y no hay masa de cresa_x000d_
+    <t>Ha subido conviviendo con gatos , perros y niños._x000D_
+Pesar alrededor de 14 kg y no hay masa de cresa_x000D_
 Está en Cádiz pero puede viajar a casi toda España con nuestros transportistas de animales</t>
   </si>
   <si>
     <t>Merlo</t>
   </si>
   <si>
-    <t>2 semanas</t>
-  </si>
-  <si>
-    <t>mix Podenco</t>
-  </si>
-  <si>
     <t>merlo</t>
   </si>
   <si>
-    <t>La madre es un podenco maneto y se desconoce al padre.
-Se entrega con protocolo veterinario completo y puede viajar a casi toda España</t>
-  </si>
-  <si>
     <t>Carpeta</t>
   </si>
   <si>
@@ -233,13 +223,24 @@
   </si>
   <si>
     <t>Judith</t>
+  </si>
+  <si>
+    <t>7 años</t>
+  </si>
+  <si>
+    <t>Fox Terrier</t>
+  </si>
+  <si>
+    <t>Pesa 7,5kd
+Tiene una ligera cojera en la patita trasera por un accidente. No le impide hacer vida normal.
+Esta dada de alta por su veterinario</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -250,6 +251,11 @@
       <sz val="11"/>
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -273,19 +279,28 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -304,12 +319,20 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
     <cellStyle name="HeaderStyle" xfId="2"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -318,10 +341,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -597,19 +620,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.85547" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.85547" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="177" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="114" customHeight="1">
+    <row r="2" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -655,7 +681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -678,7 +704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -701,27 +727,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="30">
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -730,166 +756,175 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578" customWidth="1"/>
-    <col min="2" max="2" width="36.57031" customWidth="1"/>
-    <col min="3" max="3" width="17.85547" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.57031" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="66" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>54</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
         <v>60</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
         <v>62</v>
       </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -898,21 +933,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B1">
         <v>649776448</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -920,9 +956,9 @@
         <v>692160589</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>608678808</v>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -97,141 +97,141 @@
     <t>tayson</t>
   </si>
   <si>
-    <t>Ha subido conviviendo con gatos , perros y niños._x000D_
-Pesar alrededor de 14 kg y no hay masa de cresa_x000D_
+    <t>Merlo</t>
+  </si>
+  <si>
+    <t>merlo</t>
+  </si>
+  <si>
+    <t>Carpeta</t>
+  </si>
+  <si>
+    <t>Camada</t>
+  </si>
+  <si>
+    <t>camada bodeguero breton</t>
+  </si>
+  <si>
+    <t>Blondy</t>
+  </si>
+  <si>
+    <t>blondy</t>
+  </si>
+  <si>
+    <t>Lesa</t>
+  </si>
+  <si>
+    <t>lesa</t>
+  </si>
+  <si>
+    <t>Azul y Verde</t>
+  </si>
+  <si>
+    <t>azul y verde</t>
+  </si>
+  <si>
+    <t>Dina</t>
+  </si>
+  <si>
+    <t>dina</t>
+  </si>
+  <si>
+    <t>Alba</t>
+  </si>
+  <si>
+    <t>alba</t>
+  </si>
+  <si>
+    <t>Duende</t>
+  </si>
+  <si>
+    <t>duende</t>
+  </si>
+  <si>
+    <t>Balú</t>
+  </si>
+  <si>
+    <t>balu</t>
+  </si>
+  <si>
+    <t>Camada podenco pastor aleman</t>
+  </si>
+  <si>
+    <t>camada podenco pastor aleman</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>toby</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>nico</t>
+  </si>
+  <si>
+    <t>Zule</t>
+  </si>
+  <si>
+    <t>zule</t>
+  </si>
+  <si>
+    <t>Loli</t>
+  </si>
+  <si>
+    <t>hembra mix yorki</t>
+  </si>
+  <si>
+    <t>Hera</t>
+  </si>
+  <si>
+    <t>hera</t>
+  </si>
+  <si>
+    <t>Camada amerian standfor y pitbull</t>
+  </si>
+  <si>
+    <t>camada amerian standfor pitbull</t>
+  </si>
+  <si>
+    <t>Mika</t>
+  </si>
+  <si>
+    <t>mika</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>dante</t>
+  </si>
+  <si>
+    <t>Bambi</t>
+  </si>
+  <si>
+    <t>bambi</t>
+  </si>
+  <si>
+    <t>Sira</t>
+  </si>
+  <si>
+    <t>Judith</t>
+  </si>
+  <si>
+    <t>7 años</t>
+  </si>
+  <si>
+    <t>Fox Terrier</t>
+  </si>
+  <si>
+    <t>Ha estado conviviendo con gatos , perros y niños._x000D_
+Pesa alrededor de 14kg y no va a crecer más
 Está en Cádiz pero puede viajar a casi toda España con nuestros transportistas de animales</t>
   </si>
   <si>
-    <t>Merlo</t>
-  </si>
-  <si>
-    <t>merlo</t>
-  </si>
-  <si>
-    <t>Carpeta</t>
-  </si>
-  <si>
-    <t>Camada</t>
-  </si>
-  <si>
-    <t>camada bodeguero breton</t>
-  </si>
-  <si>
-    <t>Blondy</t>
-  </si>
-  <si>
-    <t>blondy</t>
-  </si>
-  <si>
-    <t>Lesa</t>
-  </si>
-  <si>
-    <t>lesa</t>
-  </si>
-  <si>
-    <t>Azul y Verde</t>
-  </si>
-  <si>
-    <t>azul y verde</t>
-  </si>
-  <si>
-    <t>Dina</t>
-  </si>
-  <si>
-    <t>dina</t>
-  </si>
-  <si>
-    <t>Alba</t>
-  </si>
-  <si>
-    <t>alba</t>
-  </si>
-  <si>
-    <t>Duende</t>
-  </si>
-  <si>
-    <t>duende</t>
-  </si>
-  <si>
-    <t>Balú</t>
-  </si>
-  <si>
-    <t>balu</t>
-  </si>
-  <si>
-    <t>Camada podenco pastor aleman</t>
-  </si>
-  <si>
-    <t>camada podenco pastor aleman</t>
-  </si>
-  <si>
-    <t>Toby</t>
-  </si>
-  <si>
-    <t>toby</t>
-  </si>
-  <si>
-    <t>Nico</t>
-  </si>
-  <si>
-    <t>nico</t>
-  </si>
-  <si>
-    <t>Zule</t>
-  </si>
-  <si>
-    <t>zule</t>
-  </si>
-  <si>
-    <t>Loli</t>
-  </si>
-  <si>
-    <t>hembra mix yorki</t>
-  </si>
-  <si>
-    <t>Hera</t>
-  </si>
-  <si>
-    <t>hera</t>
-  </si>
-  <si>
-    <t>Camada amerian standfor y pitbull</t>
-  </si>
-  <si>
-    <t>camada amerian standfor pitbull</t>
-  </si>
-  <si>
-    <t>Mika</t>
-  </si>
-  <si>
-    <t>mika</t>
-  </si>
-  <si>
-    <t>Dante</t>
-  </si>
-  <si>
-    <t>dante</t>
-  </si>
-  <si>
-    <t>Bambi</t>
-  </si>
-  <si>
-    <t>bambi</t>
-  </si>
-  <si>
-    <t>Sira</t>
-  </si>
-  <si>
-    <t>Judith</t>
-  </si>
-  <si>
-    <t>7 años</t>
-  </si>
-  <si>
-    <t>Fox Terrier</t>
-  </si>
-  <si>
-    <t>Pesa 7,5kd
+    <t>Pesa 7,5kg
 Tiene una ligera cojera en la patita trasera por un accidente. No le impide hacer vida normal.
 Esta dada de alta por su veterinario</t>
   </si>
@@ -724,24 +724,24 @@
         <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
@@ -772,159 +772,159 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
         <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
         <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
         <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
         <v>57</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
         <v>61</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
         <v>24</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -942,7 +942,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1">
         <v>649776448</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>608678808</v>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas.github.io\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\PaginaWeb\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>Nombre</t>
   </si>
@@ -234,6 +234,18 @@
     <t>Pesa 7,5kg
 Tiene una ligera cojera en la patita trasera por un accidente. No le impide hacer vida normal.
 Esta dada de alta por su veterinario</t>
+  </si>
+  <si>
+    <t>Perla y Esmeralda</t>
+  </si>
+  <si>
+    <t>18 meses</t>
+  </si>
+  <si>
+    <t>Hembras</t>
+  </si>
+  <si>
+    <t>Rescatadas ayer después de 4 dias de intentos infructuosos, ahora en acogida temporal</t>
   </si>
 </sst>
 </file>
@@ -627,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
@@ -748,6 +760,29 @@
       </c>
       <c r="G5" s="2" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -245,7 +245,8 @@
     <t>Hembras</t>
   </si>
   <si>
-    <t>Rescatadas ayer después de 4 dias de intentos infructuosos, ahora en acogida temporal</t>
+    <t>Rescatadas ayer después de 4 dias de intentos infructuosos, ahora en acogida temporal.
+Peso:13-15 kg</t>
   </si>
 </sst>
 </file>
@@ -762,7 +763,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>68</v>
       </c>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>Nombre</t>
   </si>
@@ -247,6 +247,15 @@
   <si>
     <t>Rescatadas ayer después de 4 dias de intentos infructuosos, ahora en acogida temporal.
 Peso:13-15 kg</t>
+  </si>
+  <si>
+    <t>mix bodeguero</t>
+  </si>
+  <si>
+    <t>Yako</t>
+  </si>
+  <si>
+    <t>Bodeguerito mix de 4 añitos. Peso: solo 6 kg.  Muy espabilado y juguetón. Apto con gatos y otros perros.</t>
   </si>
 </sst>
 </file>
@@ -640,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
@@ -784,6 +793,23 @@
       </c>
       <c r="G6" s="2" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
   <si>
     <t>Nombre</t>
   </si>
@@ -796,6 +796,12 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
   <si>
     <t>Nombre</t>
   </si>
@@ -256,6 +256,18 @@
   </si>
   <si>
     <t>Bodeguerito mix de 4 añitos. Peso: solo 6 kg.  Muy espabilado y juguetón. Apto con gatos y otros perros.</t>
+  </si>
+  <si>
+    <t>Triana</t>
+  </si>
+  <si>
+    <t>45 dias</t>
+  </si>
+  <si>
+    <t>mix Bretona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hembrita de 45 dias hija de madre bretona mediana, en breve se podrá chipar y viajar a cualquier parte de España con nuestros transportistas de animales homologadosspaña </t>
   </si>
 </sst>
 </file>
@@ -649,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
@@ -816,6 +828,29 @@
       </c>
       <c r="G7" s="2" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -261,13 +261,13 @@
     <t>Triana</t>
   </si>
   <si>
-    <t>45 dias</t>
-  </si>
-  <si>
-    <t>mix Bretona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hembrita de 45 dias hija de madre bretona mediana, en breve se podrá chipar y viajar a cualquier parte de España con nuestros transportistas de animales homologadosspaña </t>
+    <t>21 dias</t>
+  </si>
+  <si>
+    <t>spirnger spaniel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hembrita de 21 dias hija de madre springer spaniel, en 1 mes se podrá chipar y viajar a cualquier parte de España con nuestros transportistas de animales homologadosspaña </t>
   </si>
 </sst>
 </file>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
   <si>
     <t>Nombre</t>
   </si>
@@ -268,6 +268,21 @@
   </si>
   <si>
     <t xml:space="preserve">Hembrita de 21 dias hija de madre springer spaniel, en 1 mes se podrá chipar y viajar a cualquier parte de España con nuestros transportistas de animales homologadosspaña </t>
+  </si>
+  <si>
+    <t>Nacho</t>
+  </si>
+  <si>
+    <t>3  años</t>
+  </si>
+  <si>
+    <t>macho</t>
+  </si>
+  <si>
+    <t>mix de pinscherNacho</t>
+  </si>
+  <si>
+    <t>Macho mix de pinscher de 3 años.Pesa unos 14 kg. Bien con niños y otros perros</t>
   </si>
 </sst>
 </file>
@@ -661,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
@@ -851,6 +866,26 @@
       </c>
       <c r="G8" s="2" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="84">
   <si>
     <t>Nombre</t>
   </si>
@@ -279,10 +279,10 @@
     <t>macho</t>
   </si>
   <si>
-    <t>mix de pinscherNacho</t>
-  </si>
-  <si>
     <t>Macho mix de pinscher de 3 años.Pesa unos 14 kg. Bien con niños y otros perros</t>
+  </si>
+  <si>
+    <t>mix de pinscher</t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="2" customWidth="1"/>
     <col min="5" max="6" width="13.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="177" style="2" customWidth="1"/>
   </cols>
@@ -694,7 +694,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -717,7 +717,7 @@
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
@@ -740,7 +740,7 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
@@ -763,7 +763,7 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
@@ -786,7 +786,7 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -809,7 +809,7 @@
       <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -822,7 +822,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -832,7 +832,7 @@
       <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -845,7 +845,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -855,7 +855,7 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -868,7 +868,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -878,14 +878,17 @@
       <c r="C9" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>82</v>
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
   <si>
     <t>Nombre</t>
   </si>
@@ -283,6 +283,57 @@
   </si>
   <si>
     <t>mix de pinscher</t>
+  </si>
+  <si>
+    <t>rita y fito</t>
+  </si>
+  <si>
+    <t>1 mes</t>
+  </si>
+  <si>
+    <t>hembra/macho</t>
+  </si>
+  <si>
+    <t>podenco maneto de para corta</t>
+  </si>
+  <si>
+    <t>Hembra Rita y macho Fito, hermanos podencos manetos.Se entregaránsobre  la tercera semana de noviembre.</t>
+  </si>
+  <si>
+    <t>Ricky</t>
+  </si>
+  <si>
+    <t>6 años</t>
+  </si>
+  <si>
+    <t>bodeguero/podenco</t>
+  </si>
+  <si>
+    <t>Mix bodeguero/podenco de 6 añitos. Peso:11 kg.</t>
+  </si>
+  <si>
+    <t>Dafne</t>
+  </si>
+  <si>
+    <t>hembra</t>
+  </si>
+  <si>
+    <t>Mestiza de Pinscher de 2 años y 6 kg</t>
+  </si>
+  <si>
+    <t>Inés y Rombo</t>
+  </si>
+  <si>
+    <t>Hembra y macho</t>
+  </si>
+  <si>
+    <t>mix Pinscher</t>
+  </si>
+  <si>
+    <t>bodegueros</t>
+  </si>
+  <si>
+    <t>Dos hermanos hembra y macho de 30 d bodegueritos.Se podran entregar sobre la tercera semana de Noviembre.</t>
   </si>
 </sst>
 </file>
@@ -676,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="2" customWidth="1"/>
@@ -889,6 +940,98 @@
       </c>
       <c r="G9" s="2" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
   <si>
     <t>Nombre</t>
   </si>
@@ -294,9 +294,6 @@
     <t>hembra/macho</t>
   </si>
   <si>
-    <t>podenco maneto de para corta</t>
-  </si>
-  <si>
     <t>Hembra Rita y macho Fito, hermanos podencos manetos.Se entregaránsobre  la tercera semana de noviembre.</t>
   </si>
   <si>
@@ -306,9 +303,6 @@
     <t>6 años</t>
   </si>
   <si>
-    <t>bodeguero/podenco</t>
-  </si>
-  <si>
     <t>Mix bodeguero/podenco de 6 añitos. Peso:11 kg.</t>
   </si>
   <si>
@@ -334,6 +328,16 @@
   </si>
   <si>
     <t>Dos hermanos hembra y macho de 30 d bodegueritos.Se podran entregar sobre la tercera semana de Noviembre.</t>
+  </si>
+  <si>
+    <t>podenco maneto de pata corta</t>
+  </si>
+  <si>
+    <t>bodeguero con podenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judith
+</t>
   </si>
 </sst>
 </file>
@@ -730,7 +734,8 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="2" customWidth="1"/>
     <col min="5" max="6" width="13.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="177" style="2" customWidth="1"/>
   </cols>
@@ -797,8 +802,8 @@
       <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
+      <c r="F3" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>18</v>
@@ -953,7 +958,7 @@
         <v>86</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>84</v>
@@ -962,76 +967,76 @@
         <v>11</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
         <v>89</v>
-      </c>
-      <c r="B11" t="s">
-        <v>90</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
       </c>
       <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="109">
   <si>
     <t>Nombre</t>
   </si>
@@ -338,6 +338,27 @@
   <si>
     <t xml:space="preserve">Judith
 </t>
+  </si>
+  <si>
+    <t>nala</t>
+  </si>
+  <si>
+    <t>scooby</t>
+  </si>
+  <si>
+    <t>camada border collie</t>
+  </si>
+  <si>
+    <t>45 dias</t>
+  </si>
+  <si>
+    <t>3hembras y 2 machos</t>
+  </si>
+  <si>
+    <t>border collie</t>
+  </si>
+  <si>
+    <t>tres hembras y do machos de 45 dias, camada de border collir puros, buscamos adopciones responsables, se entregarán a partir de 2-3 semanas</t>
   </si>
 </sst>
 </file>
@@ -731,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
@@ -878,7 +899,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1037,6 +1058,45 @@
       </c>
       <c r="G13" s="2" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -349,16 +349,16 @@
     <t>camada border collie</t>
   </si>
   <si>
-    <t>45 dias</t>
-  </si>
-  <si>
     <t>3hembras y 2 machos</t>
   </si>
   <si>
     <t>border collie</t>
   </si>
   <si>
-    <t>tres hembras y do machos de 45 dias, camada de border collir puros, buscamos adopciones responsables, se entregarán a partir de 2-3 semanas</t>
+    <t>38 dias</t>
+  </si>
+  <si>
+    <t>tres hembras y do machos de 45 dias, camada de border collie puros de Cádiz, buscamos adopciones responsables, se entregarán a partir de 2-3 semanas</t>
   </si>
 </sst>
 </file>
@@ -1081,13 +1081,13 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s">
         <v>105</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>104</v>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
   <si>
     <t>Nombre</t>
   </si>
@@ -358,7 +358,28 @@
     <t>38 dias</t>
   </si>
   <si>
-    <t>tres hembras y do machos de 45 dias, camada de border collie puros de Cádiz, buscamos adopciones responsables, se entregarán a partir de 2-3 semanas</t>
+    <t>tres hembras y do machos de 45 dias, camada de border collie puros de Cádiz, buscamos adopciones responsables, se entregarán a partir de 2-3 semanas.SOO QUEDA POR ADOPTAR EL MACHO 2 B.C.</t>
+  </si>
+  <si>
+    <t>pixel</t>
+  </si>
+  <si>
+    <t>podenquito</t>
+  </si>
+  <si>
+    <t>podenquito pequeño de 2 añitos. Ya no crece más. Muy juguetón y divertido.Está en Cádiz pero lo podemos transportar a toda España si hace falta.</t>
+  </si>
+  <si>
+    <t>harry</t>
+  </si>
+  <si>
+    <t>2 añitos</t>
+  </si>
+  <si>
+    <t>5 meses</t>
+  </si>
+  <si>
+    <t>pedenquito pequeño, muy divertido y juguetón, busca adopción responsable, está en Cádiz pero lo podemos transportar a toda españa con nuestros transportistas animalistas homologados.</t>
   </si>
 </sst>
 </file>
@@ -752,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
@@ -1076,7 +1097,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>104</v>
       </c>
@@ -1097,6 +1118,52 @@
       </c>
       <c r="G16" s="2" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="122">
   <si>
     <t>Nombre</t>
   </si>
@@ -380,6 +380,24 @@
   </si>
   <si>
     <t>pedenquito pequeño, muy divertido y juguetón, busca adopción responsable, está en Cádiz pero lo podemos transportar a toda españa con nuestros transportistas animalistas homologados.</t>
+  </si>
+  <si>
+    <t>14 meses</t>
+  </si>
+  <si>
+    <t>bodeguero</t>
+  </si>
+  <si>
+    <t>BODEGUERITO DE 14 KG QUE YA NO CRECE MAS, ATADO A UNA CADENA LA MAYOR PARTE DEL DÍA. Quieres liberarlo de esa cadena y adoptarlo responsablemente. Está en Cádiz pero podemos transportarlo a toda españa con nuestros transportistas animalistas homologados.</t>
+  </si>
+  <si>
+    <t>2,2 añitos</t>
+  </si>
+  <si>
+    <t>cruzada</t>
+  </si>
+  <si>
+    <t>Mestiza de 2,5 añitos marrón claro, muy lista y cariñosa, busca hogar responsable para siempre. Está en Cadiz y podemos transportarla a toda españa.</t>
   </si>
 </sst>
 </file>
@@ -1085,16 +1103,46 @@
       <c r="A14" t="s">
         <v>102</v>
       </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="E14" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>103</v>
       </c>
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="E15" s="1" t="s">
         <v>103</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
